--- a/SGC-CKN/Excel/de363237-6994-4044-9c82-ce3da6387d4b_Thanh_Hoá_P11-65_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/de363237-6994-4044-9c82-ce3da6387d4b_Thanh_Hoá_P11-65_D800_28-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">05:00
@@ -112,20 +112,17 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">06:00
 28/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài lớp tính từ 1.1 đến 12.8</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">07:00
@@ -135,7 +132,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
@@ -155,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -165,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">09:46
@@ -178,7 +175,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13:43
@@ -1154,19 +1151,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="8">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1189,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="G12" s="9">
         <v>-12.8</v>
@@ -1198,30 +1195,30 @@
         <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>11.7</v>
+        <v>9.5</v>
       </c>
       <c r="J12" s="12">
-        <v>23.4</v>
+        <v>19</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-12.8</v>
@@ -1244,19 +1241,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-18.8</v>
@@ -1279,19 +1276,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-27.2</v>
@@ -1314,19 +1311,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-34.3</v>
@@ -1349,19 +1346,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-38.2</v>
@@ -1379,24 +1376,24 @@
         <v>8.2</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>52</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-44.49</v>
@@ -1414,12 +1411,12 @@
         <v>1.3</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1525,31 +1522,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1566,19 +1563,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="G2" s="5">
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="I2" s="8">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1595,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="F3" s="9">
         <v>-12.8</v>
@@ -1604,10 +1601,10 @@
         <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>11.7</v>
+        <v>9.5</v>
       </c>
       <c r="I3" s="12">
-        <v>23.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1618,7 +1615,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1647,7 +1644,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1676,7 +1673,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1705,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1734,7 +1731,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1763,7 +1760,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1786,7 +1783,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1798,7 +1795,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="F10" s="33">
         <v>-49.64</v>
@@ -1807,10 +1804,10 @@
         <v>8.72</v>
       </c>
       <c r="H10" s="33">
-        <v>49.64</v>
+        <v>48.54</v>
       </c>
       <c r="I10" s="33">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
     </row>
   </sheetData>
